--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_107_R11.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_107_R11.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.3945</v>
+        <v>7.6276</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5982</v>
+        <v>6.6296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7963</v>
+        <v>0.9979</v>
       </c>
       <c r="G2" t="n">
         <v>6.3452</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2548</v>
+        <v>-0.0217</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1221</v>
+        <v>0.1535</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3769</v>
+        <v>-0.1753</v>
       </c>
       <c r="V2" t="n">
         <v>1.0722</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0643</v>
+        <v>5.2391</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7735</v>
+        <v>3.2146</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2908</v>
+        <v>2.0245</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6085</v>
+        <v>3.0935</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5315</v>
+        <v>1.059</v>
       </c>
       <c r="I3" t="n">
-        <v>0.077</v>
+        <v>2.0344</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9261</v>
+        <v>2.7974</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2106</v>
+        <v>1.5461</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.2845</v>
+        <v>1.2514</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6824</v>
+        <v>0.2961</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3209</v>
+        <v>-0.487</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3615</v>
+        <v>0.7831</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3863</v>
+        <v>0.1483</v>
       </c>
       <c r="T3" t="n">
-        <v>2.2571</v>
+        <v>0.2754</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1292</v>
+        <v>-0.1272</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.1418</v>
       </c>
       <c r="W3" t="n">
-        <v>1.7501</v>
+        <v>0.1418</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2066</v>
+        <v>4.4189</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2829</v>
+        <v>2.4642</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9237</v>
+        <v>1.9548</v>
       </c>
       <c r="G4" t="n">
-        <v>3.0935</v>
+        <v>1.6085</v>
       </c>
       <c r="H4" t="n">
-        <v>1.059</v>
+        <v>1.5315</v>
       </c>
       <c r="I4" t="n">
-        <v>2.0344</v>
+        <v>0.077</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7974</v>
+        <v>0.9261</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5461</v>
+        <v>1.2106</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2514</v>
+        <v>-0.2845</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2961</v>
+        <v>0.6824</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.487</v>
+        <v>0.3209</v>
       </c>
       <c r="O4" t="n">
-        <v>0.7831</v>
+        <v>0.3615</v>
       </c>
       <c r="P4" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.8843</v>
+        <v>0.7409</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6563</v>
+        <v>0.9478</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.228</v>
+        <v>-0.2069</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1418</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1418</v>
+        <v>1.7501</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6232</v>
+        <v>1.4677</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2107</v>
+        <v>0.9161</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5874</v>
+        <v>0.5516</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0669</v>
+        <v>1.5678</v>
       </c>
       <c r="H5" t="n">
-        <v>2.432</v>
+        <v>0.3732</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.365</v>
+        <v>1.1946</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3896</v>
+        <v>2.1041</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0655</v>
+        <v>0.5349</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.5692</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3226</v>
+        <v>-0.5363</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6335</v>
+        <v>-0.1617</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6891</v>
+        <v>-0.3746</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3917</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-2.5515</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1672</v>
+        <v>-0.4944</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8417</v>
+        <v>0.2912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3255</v>
+        <v>-0.7857</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.0026</v>
+        <v>0.3943</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.7886</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5708</v>
+        <v>0.8894</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4561</v>
+        <v>1.5776</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1147</v>
+        <v>-0.6883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5678</v>
+        <v>1.0669</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3732</v>
+        <v>2.432</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1946</v>
+        <v>-1.365</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1041</v>
+        <v>2.3896</v>
       </c>
       <c r="K6" t="n">
-        <v>0.5349</v>
+        <v>3.0655</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5692</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5363</v>
+        <v>-1.3226</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1617</v>
+        <v>-0.6335</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3746</v>
+        <v>-0.6891</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.3913</v>
+        <v>0.4334</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1687</v>
+        <v>0.2087</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.2226</v>
+        <v>0.2247</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3943</v>
+        <v>-2.0026</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>-0.7886</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2566</v>
+        <v>-1.0629</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6442</v>
+        <v>2.0457</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9008</v>
+        <v>-3.1086</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6919</v>
+        <v>-1.5211</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.377</v>
+        <v>0.6135</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3149</v>
+        <v>-2.1347</v>
       </c>
       <c r="J7" t="n">
-        <v>0.306</v>
+        <v>0.4804</v>
       </c>
       <c r="K7" t="n">
-        <v>0.306</v>
+        <v>1.1932</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.7127</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9979</v>
+        <v>-2.0016</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.5796</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3149</v>
+        <v>-1.422</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4353</v>
+        <v>-0.168</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5702</v>
+        <v>0.1889</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1349</v>
+        <v>-0.3569</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5683</v>
+        <v>-1.5768</v>
       </c>
       <c r="E8" t="n">
-        <v>1.5739</v>
+        <v>0.2904</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.1422</v>
+        <v>-1.8672</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5211</v>
+        <v>-1.6919</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6135</v>
+        <v>-0.377</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.1347</v>
+        <v>-1.3149</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4804</v>
+        <v>0.306</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1932</v>
+        <v>0.306</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7127</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0016</v>
+        <v>-1.9979</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5796</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.422</v>
+        <v>-1.3149</v>
       </c>
       <c r="P8" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6734</v>
+        <v>0.1151</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2829</v>
+        <v>0.2164</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3905</v>
+        <v>-0.1013</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.9322</v>
+        <v>-2.2939</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6417</v>
+        <v>-0.9026</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2905</v>
+        <v>-1.3913</v>
       </c>
       <c r="G9" t="n">
         <v>-1.3848</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5627</v>
+        <v>0.0756</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3576</v>
+        <v>0.3815</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2051</v>
+        <v>-0.306</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1444</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.0174</v>
+        <v>-4.5039</v>
       </c>
       <c r="E10" t="n">
-        <v>-6.6753</v>
+        <v>-5.8929</v>
       </c>
       <c r="F10" t="n">
-        <v>1.6579</v>
+        <v>1.389</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0049</v>
@@ -1234,13 +1234,13 @@
         <v>2.0876</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3014</v>
+        <v>0.2122</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.731</v>
+        <v>0.0514</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4296</v>
+        <v>0.1608</v>
       </c>
       <c r="V10" t="n">
         <v>1.0722</v>
@@ -1267,28 +1267,28 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>9.084899999999999</v>
+        <v>10.2052</v>
       </c>
       <c r="E11" t="n">
-        <v>9.222500000000002</v>
+        <v>10.3427</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1375</v>
+        <v>-0.1375999999999993</v>
       </c>
       <c r="G11" t="n">
-        <v>6.079200000000001</v>
+        <v>6.079200000000003</v>
       </c>
       <c r="H11" t="n">
         <v>5.8278</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2511999999999999</v>
+        <v>0.2512000000000003</v>
       </c>
       <c r="J11" t="n">
         <v>12.9263</v>
       </c>
       <c r="K11" t="n">
-        <v>9.480600000000003</v>
+        <v>9.480600000000001</v>
       </c>
       <c r="L11" t="n">
         <v>3.445700000000001</v>
@@ -1312,16 +1312,16 @@
         <v>13.9173</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.07909999999999984</v>
+        <v>1.0414</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5946</v>
+        <v>2.7148</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6737</v>
+        <v>-1.6738</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3943000000000005</v>
+        <v>-0.3943000000000003</v>
       </c>
       <c r="W11" t="n">
         <v>5.139600000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.9874</v>
+        <v>3.1175</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4669</v>
+        <v>4.5848</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4795</v>
+        <v>-1.4674</v>
       </c>
       <c r="G12" t="n">
         <v>3.2644</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2254</v>
+        <v>-0.0953</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2513</v>
+        <v>-0.1333</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0259</v>
+        <v>0.038</v>
       </c>
       <c r="V12" t="n">
         <v>-0.2836</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2231</v>
+        <v>2.6962</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7232</v>
+        <v>2.195</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4999</v>
+        <v>0.5012</v>
       </c>
       <c r="G13" t="n">
         <v>0.5634</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1959</v>
+        <v>0.2772</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6247</v>
+        <v>-0.1529</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4288</v>
+        <v>0.4301</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4904</v>
+        <v>1.9</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1481</v>
+        <v>1.266</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3423</v>
+        <v>0.634</v>
       </c>
       <c r="G14" t="n">
         <v>1.3261</v>
@@ -1546,13 +1546,13 @@
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2996</v>
+        <v>0.11</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2249</v>
+        <v>0.0668</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8168</v>
+        <v>0.8006</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8134</v>
+        <v>2.2892</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9966</v>
+        <v>-1.4886</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6249</v>
+        <v>0.0582</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.7588</v>
+        <v>-1.0359</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1339</v>
+        <v>1.0941</v>
       </c>
       <c r="J15" t="n">
-        <v>1.2912</v>
+        <v>1.4958</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6288</v>
+        <v>-0.0231</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6625</v>
+        <v>1.5189</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.9161</v>
+        <v>-1.4376</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3875</v>
+        <v>-1.0127</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5286</v>
+        <v>-0.4248</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5292</v>
+        <v>-0.4353</v>
       </c>
       <c r="T15" t="n">
-        <v>1.7695</v>
+        <v>-0.2787</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2403</v>
+        <v>-0.1566</v>
       </c>
       <c r="V15" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.0722</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0358</v>
+        <v>0.2264</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9354</v>
+        <v>0.9878</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9712</v>
+        <v>-0.7614</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0582</v>
+        <v>-0.6249</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.0359</v>
+        <v>-0.7588</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0941</v>
+        <v>0.1339</v>
       </c>
       <c r="J16" t="n">
-        <v>1.4958</v>
+        <v>1.2912</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.0231</v>
+        <v>0.6288</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5189</v>
+        <v>0.6625</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4376</v>
+        <v>-1.9161</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0127</v>
+        <v>-1.3875</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4248</v>
+        <v>-0.5286</v>
       </c>
       <c r="P16" t="n">
-        <v>1.8556</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2718</v>
+        <v>0.9388</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6326000000000001</v>
+        <v>0.9438</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6392</v>
+        <v>-0.005</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6778999999999999</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
         <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7501</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.287</v>
+        <v>0.1962</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7362</v>
+        <v>0.9721</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0232</v>
+        <v>-0.7759</v>
       </c>
       <c r="G17" t="n">
         <v>1.7888</v>
@@ -1780,13 +1780,13 @@
         <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5913</v>
+        <v>-0.1081</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4007</v>
+        <v>-0.1647</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1906</v>
+        <v>0.0567</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7886</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0227</v>
+        <v>-0.9162</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.471</v>
+        <v>-0.5889</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5517</v>
+        <v>-0.3272</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7071</v>
@@ -1858,13 +1858,13 @@
         <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2179</v>
+        <v>0.3244</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2047</v>
+        <v>0.0868</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0132</v>
+        <v>0.2377</v>
       </c>
       <c r="V18" t="n">
         <v>0.9304</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7473</v>
+        <v>-2.4436</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.5056</v>
+        <v>-2.4492</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2417</v>
+        <v>0.0057</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2469</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>1.3706</v>
+        <v>0.6743</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6201</v>
+        <v>0.6765</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2495</v>
+        <v>-0.0022</v>
       </c>
       <c r="V19" t="n">
         <v>1.0722</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.3658</v>
+        <v>-3.636</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3522</v>
+        <v>-2.8804</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0137</v>
+        <v>-0.7556</v>
       </c>
       <c r="G20" t="n">
         <v>-4.209</v>
@@ -2014,13 +2014,13 @@
         <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3888</v>
+        <v>0.3411</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2908</v>
+        <v>0.181</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.098</v>
+        <v>0.1601</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.144</v>
+        <v>-8.6671</v>
       </c>
       <c r="E21" t="n">
-        <v>-6.3569</v>
+        <v>-6.2389</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7871</v>
+        <v>-2.4282</v>
       </c>
       <c r="G21" t="n">
         <v>-6.2921</v>
@@ -2092,13 +2092,13 @@
         <v>0.4639</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.0659</v>
+        <v>0.411</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3541</v>
+        <v>0.472</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.42</v>
+        <v>-0.0611</v>
       </c>
       <c r="V21" t="n">
         <v>-0.9304</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.084900000000001</v>
+        <v>-6.725999999999999</v>
       </c>
       <c r="E22" t="n">
         <v>0.1375000000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>-9.2225</v>
+        <v>-6.8634</v>
       </c>
       <c r="G22" t="n">
-        <v>-6.0791</v>
+        <v>-6.079099999999999</v>
       </c>
       <c r="H22" t="n">
         <v>-5.8279</v>
@@ -2149,7 +2149,7 @@
         <v>3.652700000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>3.1943</v>
+        <v>3.194300000000001</v>
       </c>
       <c r="M22" t="n">
         <v>-12.9261</v>
@@ -2170,16 +2170,16 @@
         <v>10.438</v>
       </c>
       <c r="S22" t="n">
-        <v>0.07899999999999986</v>
+        <v>2.4381</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6736</v>
+        <v>1.6738</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5946</v>
+        <v>0.7645</v>
       </c>
       <c r="V22" t="n">
-        <v>0.3943000000000002</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
         <v>5.533900000000001</v>
